--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/_main.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/_main.xlsx
@@ -15562,6 +15562,18 @@
         </is>
       </c>
     </row>
+    <row r="277" ht="12.8" customHeight="1" s="13">
+      <c r="D277" s="11" t="inlineStr">
+        <is>
+          <t>getAchievement</t>
+        </is>
+      </c>
+      <c r="E277" s="11" t="inlineStr">
+        <is>
+          <t>ONEV</t>
+        </is>
+      </c>
+    </row>
     <row r="282" ht="12.8" customHeight="1" s="13">
       <c r="B282" s="11" t="inlineStr">
         <is>
@@ -29163,7 +29175,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>(Após se despedir de Ash e Fiama, em breve)</t>
+          <t>(Após partir com Ash e Fiama, em breve)</t>
         </is>
       </c>
     </row>

--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/_main.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/_main.xlsx
@@ -15562,18 +15562,6 @@
         </is>
       </c>
     </row>
-    <row r="277" ht="12.8" customHeight="1" s="13">
-      <c r="D277" s="11" t="inlineStr">
-        <is>
-          <t>getAchievement</t>
-        </is>
-      </c>
-      <c r="E277" s="11" t="inlineStr">
-        <is>
-          <t>ONEV</t>
-        </is>
-      </c>
-    </row>
     <row r="282" ht="12.8" customHeight="1" s="13">
       <c r="B282" s="11" t="inlineStr">
         <is>
@@ -29175,7 +29163,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>(Após partir com Ash e Fiama, em breve)</t>
+          <t>(Após se despedir de Ash e Fiama, em breve)</t>
         </is>
       </c>
     </row>
